--- a/Result/checksun_type/貨櫃航運.xlsx
+++ b/Result/checksun_type/貨櫃航運.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>43.54</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>44.11</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>44.11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>490057.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>805691.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>805691.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1303801.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1943788.48</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1943788.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-327585.8476253878</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>490057</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>490057.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>43.92</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>43.49</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>44.13</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>44.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1583750.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>988492.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>988492.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1433201.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1962099.68</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1962099.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-286606.2440955555</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1583750</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1583750.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>43.92</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>43.44</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>44.15</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>44.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>662684.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1002672.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1002672</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1878900.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1932234.52</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1932234.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-335009.4089066682</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>662684</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>662684.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>43.95</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>43.4</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>44.17</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>669578.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1346024.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1346024.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2567374.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1964625.26</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1964625.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-293506.522604448</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>669578</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>669578.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>43.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>43.37</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>44.21</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>44.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>622390.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1452261.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1452261.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2829191.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1985574.38</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1985574.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-224472.9520796891</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>622390</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>622390.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>43.97000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>43.35</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>44.23</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44.23</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1404060.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1801911.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1801911.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>3022377.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2002187.04</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2002187.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-112780.8173271874</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1404060</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1404060.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>43.98999999999999</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>43.34</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>44.26</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>44.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1654648.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1877910.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1877910.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>3157131.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2013435.62</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2013435.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-32943.0956333573</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1654648</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1654648.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>43.92</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>43.31</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>44.28</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>44.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>2379448.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>2755129.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>2755129.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>3126842.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2008212.78</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2008212.78</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>55438.61734473472</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>2379448</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2379448.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>43.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>44.3</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1200760.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3788724.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3788724</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>3111702.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1984167.88</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1984167.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>102061.1138368398</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1200760</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1200760.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>43.58</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>44.32</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>44.32</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2370642.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>4206122.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>4206122</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>3077742.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1975864.68</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1975864.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>291307.6404742454</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2370642</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2370642.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>43.28</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>44.35</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1784056.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4242843.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4242843</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3117699.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1949494.58</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1949494.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>425911.4770821738</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1784056</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1784056.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>80.44000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>81.81</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>79.33</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>79.33</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2333076095.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2912020097.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2912020097.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2914681397.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1468206020.76</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1468206020.76</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>176748571.6688733</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2333076095</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2333076095.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>80.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>79.26</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>81.65000000000001</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>79.26000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1899958921.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3240132756.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3240132756</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2924419799.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1433882262.04</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1433882262.04</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>241766018.4694448</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1899958921</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1899958921.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>81.35999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>81.62</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>79.31</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>81.62</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>79.31</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>3337074951.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3593935520.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3593935520.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2806274758.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1405398919.02</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1405398919.02</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>372418996.1677809</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>3337074951</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>3337074951.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>81.74</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>81.51</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>79.34</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>79.34</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3959184133.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3345007637.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3345007637.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2572694108.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1345513817.56</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1345513817.56</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>391788711.2308407</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3959184133</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3959184133.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>82.3</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>81.37</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>79.39</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>81.37</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>79.39</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>3030806389.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3240659096.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3240659096.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2264527646.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1272033764.12</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1272033764.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>338812723.5626812</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>3030806389</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>3030806389.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>82.7</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>81.18</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>3973639386.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2917342697.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>2917342697.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2055619069.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1219195791.68</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1219195791.68</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>350501330.766644</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>3973639386</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>3973639386.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>82.52</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>80.94</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>3668972744.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2608706842.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2608706842</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1740720357.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1149123248.08</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1149123248.08</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>253663615.2806392</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>3668972744</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>3668972744.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>81.67999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>80.74</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>79.35</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>79.34999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>2092435535.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2018613995.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2018613995.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1470286627.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1081088777.68</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1081088777.68</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>138907461.3977518</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>2092435535</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2092435535.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>81.4</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>80.68</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>79.33</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>79.33</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>3437441429.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1800380580.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1800380580.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1459119274.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1049965351.02</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1049965351.02</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>138923818.9079933</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>3437441429</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>3437441429.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>81.41999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>80.53</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>79.31</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>80.53</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>79.31</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1414224394.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1288396195.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1288396195.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1528754002.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>994318012.32</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>994318012.3200001</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-10122152.53837609</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1414224394</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1414224394.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>81.24</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>80.37</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>79.29</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>80.37</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>79.29000000000001</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2430460108.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1193895440.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1193895440.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1928016666.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>979873490.64</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>979873490.64</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-5910209.692533016</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2430460108</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2430460108.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>53.78</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>54.04</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>54.04</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1363134312.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1172735370.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1172735370.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1070102595.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1238264245.38</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1238264245.38</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-18242658.1647625</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1363134312</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1363134312.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>51.54</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>54.1</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>837571860.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1149758704.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1149758704.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1032732902.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1235298680.86</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1235298680.86</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-44263019.39978361</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>837571860</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>837571860.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>51.6</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>54.17</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>54.21</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>54.21</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1388361285.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1256317202.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1256317202</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1000368735.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1233930075.38</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1233930075.38</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-23543879.18553567</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1388361285</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1388361285.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>51.76000000000001</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>54.27</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>54.3</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1372820539.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>1106665322.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>1106665322.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>935406113.7</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1220973530.8</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1220973530.8</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-52117407.30141258</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1372820539</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1372820539.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>52.3</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>54.42</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>54.44</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>54.44</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>901788855.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1014376583.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1014376583.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>857121338.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1206429651.06</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1206429651.06</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-89410317.27761483</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>901788855</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>901788855.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>52.82000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>54.54</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>54.56</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>54.56</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1248250982.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>967469821.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>967469821.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>835481892.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1198443193.04</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1198443193.04</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-89024996.9122746</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1248250982</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1248250982.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>53.34</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>54.69</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>54.69</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1370364349.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>915707101.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>915707101.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>801066109.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1188559662.56</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1188559662.56</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-122416017.2506361</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1370364349</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1370364349.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>53.56</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>54.77</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>54.81</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>54.81</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>640101886.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>744420268.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>744420268.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>754504371.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1169914725.78</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1169914725.78</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-178829049.2964869</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>640101886</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>640101886.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>53.54000000000001</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>54.82</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>54.89</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>54.89</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>911376845.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>764146905.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>764146905.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>840580970.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1169898999.4</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1169898999.4</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-174789936.5656847</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>911376845</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>911376845.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>53.66</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>54.8</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>54.96</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>54.96</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>667255046.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>699866094.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>699866094.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1052154842.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1171425869.94</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1171425869.94</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-191842451.9657644</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>667255046</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>667255046.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>53.82000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>54.75</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>55.03</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>55.03</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>989437380.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>703493963.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>703493963</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1692858407.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1186173275.1</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1186173275.1</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-183195765.0742438</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>989437380</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>989437380.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>58.14</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>57.65</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>50.76</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>50.76</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>56864083.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>49667804.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>49667804.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>55100193.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>65077891.96</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>65077891.96</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1281965.690591685</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>56864083</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>56864083.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>57.72000000000001</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>50.25</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>50.25</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>34267315.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>50744106.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>50744106.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>54082868.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>64807510.26</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>64807510.26</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1866398.578095213</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>34267315</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>34267315.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>57.32000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>57.58</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>49.75</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>57923106.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>66727550.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>66727550.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>54074047.8</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>65417577.8</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>65417577.8</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-213563.3253111318</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>57923106</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>57923106.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>57.17999999999999</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>49.27</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>49.27</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>53259597.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>64935816.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>64935816.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>53469700.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>65166202.68</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>65166202.68</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-379291.8811441883</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>53259597</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>53259597.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>57.08</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>57.51</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>48.8</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>46024921.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>62159314.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>62159314.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>50977637.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>65142686.74</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>65142686.74</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-102839.1437219754</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>46024921</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>46024921.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>56.94</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>57.45</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>48.34</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>48.34</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>62245593.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>60532582.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>60532582.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>52060465.0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>65076480.76</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>65076480.76</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>1070910.022014104</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>62245593</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>62245593.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>56.94</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>57.42</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>47.88</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>47.88</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>114184535.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>57421631.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>57421631</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>51090635.9</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>65160318.42</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>65160318.42</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>971518.6151365787</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>114184535</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>114184535.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>57.02</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>47.45</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>47.45</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>48964435.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>41420545.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>41420545.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>44543610.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>65562718.96</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>65562718.96</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-4770052.845229052</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>48964435</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>48964435.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>57.08</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>47.01</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>47.01</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>39377089.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>42003583.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>42003583.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>42069892.1</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>66086974.4</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>66086974.4</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-5814070.901278906</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>39377089</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>39377089.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>57.36</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>57.61</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>46.57</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>46.57</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>37891260.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>39795960.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>39795960.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>44332954.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>66156768.56</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>66156768.56</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-6070664.23487588</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>37891260</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>37891260.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>57.73999999999999</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>46.14</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>46.14</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>46690836.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>43588347.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>43588347.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>51191973.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>66777211.68</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>66777211.68</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-6061220.738768853</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>46690836</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>46690836.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>180.8</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>184.88</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>183.68</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>184.88</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>183.68</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>1653699443.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>1433704375.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>1433704375.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1795280026.1</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>2187264744.9</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>2187264744.9</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-190679631.2541761</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>1653699443</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>1653699443.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>180.3</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>185.28</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>183.7</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>185.28</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>183.7</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>1077883649.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>1393514240.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>1393514240.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>1889399838.6</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>2184416480.12</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>2184416480.12</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-216567940.2490144</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>1077883649</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>1077883649.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>180.1</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>185.62</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>183.8</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>185.62</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>183.8</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1661563788.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>1628273425.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>1628273425</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1977600044.4</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>2187824437.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>2187824437</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-184122120.1613183</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1661563788</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1661563788.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>180.6</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>185.95</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>183.91</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>185.95</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>183.91</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>1425055671.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1648369344.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1648369344</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>2017119695.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>2182639129.88</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>2182639129.88</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-193732316.3517053</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1425055671</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1425055671.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>181.7</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>186.2</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>184.04</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>184.04</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1350319325.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1939756484.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1939756484.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1980139332.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>2179310612.1</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>2179310612.1</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-175202001.3611259</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1350319325</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1350319325.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>182.7</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>186.2</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>184.12</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>184.12</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1452748769.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>2156855677.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>2156855677</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1953974951.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>2171643869.86</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>2171643869.86</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-134465442.8259721</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1452748769</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1452748769.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>184.0</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>186.32</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>184.23</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>186.32</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>184.23</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>2251679572.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>2385285436.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>2385285436.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1990225151.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>2173840051.4</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>2173840051.4</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-82442605.24625301</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>2251679572</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>2251679572.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>184.1</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>186.58</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>184.3</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>186.58</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>184.3</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>1762043383.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>2326926663.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>2326926663.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>2053012319.5</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>2152745989.62</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>2152745989.62</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-90779615.98071718</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>1762043383</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>1762043383.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>184.3</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>186.82</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>184.33</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>186.82</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>184.33</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>2881991375.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>2385870047.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>2385870047.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>2078510060.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2155425351.4</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2155425351.4</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-46986481.9234972</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>2881991375</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>2881991375.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>184.6</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>186.82</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>184.3</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>186.82</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>184.3</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>2435815286.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>2020522179.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>2020522179.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>2201734825.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2136172608.1</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2136172608.1</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-102741200.915915</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>2435815286</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>2435815286.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>184.8</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>186.65</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>184.26</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>186.65</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>184.26</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>2594897568.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1751094225.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1751094225.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>2941763359.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>2134682988.7</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>2134682988.7</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-130916889.9080863</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>2594897568</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>2594897568.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
